--- a/data/dividends_info_20260729.xlsx
+++ b/data/dividends_info_20260729.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.9900016784668</v>
+        <v>42.89500045776367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.204591944910189</v>
+        <v>0.209814661474635</v>
       </c>
       <c r="J2" t="n">
         <v>229</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>63.45000076293945</v>
+        <v>64.94999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.103230877199395</v>
+        <v>1.077752167652634</v>
       </c>
       <c r="J3" t="n">
         <v>208</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6651884363083036</v>
       </c>
       <c r="J4" t="n">
         <v>138</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.9900016784668</v>
+        <v>42.89500045776367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.204591944910189</v>
+        <v>0.209814661474635</v>
       </c>
       <c r="J6" t="n">
         <v>138</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.095000028610229</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>3.675417610904753</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J7" t="n">
         <v>117</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.06999969482422</v>
+        <v>23.57500076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1703511208133</v>
+        <v>1.145280980963731</v>
       </c>
       <c r="J8" t="n">
         <v>117</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.010000228881836</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I9" t="n">
-        <v>3.327786894896843</v>
+        <v>3.389830453681454</v>
       </c>
       <c r="J9" t="n">
         <v>110</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.699999809265137</v>
+        <v>7.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7792207985226717</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>82</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.06999969482422</v>
+        <v>23.57500076293945</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1703511208133</v>
+        <v>1.145280980963731</v>
       </c>
       <c r="J14" t="n">
         <v>54</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.988999962806702</v>
+        <v>2.016000032424927</v>
       </c>
       <c r="I15" t="n">
-        <v>2.865761742879402</v>
+        <v>2.827380906905943</v>
       </c>
       <c r="J15" t="n">
         <v>54</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>43.9900016784668</v>
+        <v>42.89500045776367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.204591944910189</v>
+        <v>0.209814661474635</v>
       </c>
       <c r="J16" t="n">
         <v>54</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>93.19999694824219</v>
+        <v>92.30000305175781</v>
       </c>
       <c r="I17" t="n">
-        <v>1.427038673336657</v>
+        <v>1.440953365141488</v>
       </c>
       <c r="J17" t="n">
         <v>54</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.739999771118164</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I18" t="n">
-        <v>5.226481044642261</v>
+        <v>5.172413623006964</v>
       </c>
       <c r="J18" t="n">
         <v>47</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.900000095367432</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I20" t="n">
-        <v>7.586206647076882</v>
+        <v>8.20895501940042</v>
       </c>
       <c r="J20" t="n">
         <v>12</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.990000009536743</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="I23" t="n">
-        <v>4.94879597083766</v>
+        <v>4.915913636837809</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.570000171661377</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="I24" t="n">
-        <v>4.488330202787623</v>
+        <v>4.448398667095876</v>
       </c>
       <c r="J24" t="n">
         <v>-2</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.070000171661377</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="I25" t="n">
-        <v>3.439803294722022</v>
+        <v>3.535353501297214</v>
       </c>
       <c r="J25" t="n">
         <v>-9</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9.840000152587891</v>
+        <v>9.829000473022461</v>
       </c>
       <c r="I26" t="n">
-        <v>2.642276381790714</v>
+        <v>2.645233365423258</v>
       </c>
       <c r="J26" t="n">
         <v>-9</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13.39999961853027</v>
+        <v>13.64000034332275</v>
       </c>
       <c r="I27" t="n">
-        <v>4.477612067766676</v>
+        <v>4.398826868752393</v>
       </c>
       <c r="J27" t="n">
         <v>-9</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.631999969482422</v>
+        <v>2.605999946594238</v>
       </c>
       <c r="I28" t="n">
-        <v>8.35866271089899</v>
+        <v>8.442056965024744</v>
       </c>
       <c r="J28" t="n">
         <v>-9</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6.5</v>
+        <v>6.505000114440918</v>
       </c>
       <c r="I30" t="n">
-        <v>3.692307692307692</v>
+        <v>3.689469573831471</v>
       </c>
       <c r="J30" t="n">
         <v>-9</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="I31" t="n">
-        <v>1.928205128205128</v>
+        <v>1.978947368421053</v>
       </c>
       <c r="J31" t="n">
         <v>-9</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.679999828338623</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I33" t="n">
-        <v>2.112676120187481</v>
+        <v>2.120141399913057</v>
       </c>
       <c r="J33" t="n">
         <v>-16</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8.5</v>
+        <v>8.449999809265137</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5917159896876767</v>
       </c>
       <c r="J34" t="n">
         <v>-16</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.119999885559082</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I36" t="n">
-        <v>4.009434178699683</v>
+        <v>4.047619231433834</v>
       </c>
       <c r="J36" t="n">
         <v>-23</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.239999771118164</v>
+        <v>4.420000076293945</v>
       </c>
       <c r="I37" t="n">
-        <v>1.650943485346928</v>
+        <v>1.583710379903278</v>
       </c>
       <c r="J37" t="n">
         <v>-23</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>34.79999923706055</v>
+        <v>35.25</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4310344922084259</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="J38" t="n">
         <v>-23</v>
@@ -2332,7 +2332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C175"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,14 +3283,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3300,14 +3300,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3317,14 +3317,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3334,14 +3334,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3426,7 +3426,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3470,14 +3470,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3562,7 +3562,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3589,14 +3589,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3606,14 +3606,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3681,7 +3681,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3946,14 +3946,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3980,14 +3980,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3997,14 +3997,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4014,14 +4014,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4055,7 +4055,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4065,14 +4065,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4082,14 +4082,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4106,7 +4106,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4123,7 +4123,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4133,14 +4133,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4218,14 +4218,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4242,7 +4242,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4269,14 +4269,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4293,7 +4293,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4320,14 +4320,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4371,14 +4371,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4395,7 +4395,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4405,14 +4405,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4480,7 +4480,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4507,14 +4507,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4524,14 +4524,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4541,14 +4541,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4558,14 +4558,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4582,7 +4582,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4650,7 +4650,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4660,14 +4660,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4701,7 +4701,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4718,7 +4718,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4728,14 +4728,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4769,7 +4769,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4786,7 +4786,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4820,7 +4820,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4830,14 +4830,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4847,14 +4847,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4864,14 +4864,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4888,7 +4888,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4898,14 +4898,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4915,14 +4915,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4949,14 +4949,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4966,14 +4966,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5000,14 +5000,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5051,14 +5051,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5068,14 +5068,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5102,14 +5102,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5119,14 +5119,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5136,14 +5136,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5153,14 +5153,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5194,7 +5194,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5204,14 +5204,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5238,73 +5238,243 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
+          <t>Riba Mundo Tecnologia S.A.</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Unipol S.p.A.</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>eVISO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Annual Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Aquafil S.p.A.</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Sesa S.p.A.</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Sesa S.p.A.</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
           <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>Half Year Preliminary Results</t>
         </is>
@@ -5321,104 +5491,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0003073266</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1.988999962806702</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2.865761742879402</v>
-      </c>
-      <c r="I2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5429,95 +5504,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ECOSUNTEK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>First Point S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sesa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>